--- a/Logics.xlsx
+++ b/Logics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumit.raj\Desktop\SDE\DSA-github\leetcode_dsa-java\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C6728-9399-4262-9424-4CBABBCD9281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEB6AD1-8643-4D33-BAE9-959466CBA97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="205">
   <si>
     <t>LOGIC</t>
   </si>
@@ -703,6 +703,12 @@
   </si>
   <si>
     <t>1. Each character of a word is stored as a path in a tree where every node has 26 possible children (a–z). 2. insert() builds this path by creating missing nodes and marking the last node as an end-of-word. 3. search() follows the same path and returns true only if the entire path exists and the final node is marked as an end-of-word. 4. startsWith() checks only whether the prefix path exists, without needing the end-of-word flag.</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/island-perimeter/description/</t>
+  </si>
+  <si>
+    <t>Traverse each cell in matrix, if its 1 then add its perimeter to result, then check its top and right if its land too since they are only already visited neighbours ,and subtract per-=2 because the side of this current land is shared with other lands (already calculated in other land). We are not chekcing right and bottom because we have not visited them and thier perimeter doesnt included in the current perimeter, and inluding those side will leads to duplicate calculations in the current perimiter.</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -2173,6 +2179,17 @@
       </c>
       <c r="J102" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G103" t="s">
+        <v>4</v>
+      </c>
+      <c r="I103" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2257,6 +2274,7 @@
     <hyperlink ref="A100" r:id="rId78" xr:uid="{27B6E1F3-5A51-4799-A52D-0E00ECF9057E}"/>
     <hyperlink ref="A101" r:id="rId79" xr:uid="{BBCECA0C-7F19-47DD-ACD3-DF51E2D86AF5}"/>
     <hyperlink ref="A102" r:id="rId80" xr:uid="{F4F40314-DC79-4B53-92AC-6E7C67CF539A}"/>
+    <hyperlink ref="A103" r:id="rId81" xr:uid="{072B681F-C424-482B-B890-1D7FC5FD0128}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
